--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260625.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260625.xlsx
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>146,265,822</t>
+          <t>129,109,547</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>129,109,547</t>
+          <t>146,265,822</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
